--- a/products/Editors/scenarios/smoke/4. Ввод текста в редакторе документов.xlsx
+++ b/products/Editors/scenarios/smoke/4. Ввод текста в редакторе документов.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Тестирование редактора\test_cases\smoke\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Testing\products\Editors\scenarios\smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37F3843-79F0-4E6E-BE58-72DC01482959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB7F5BD-B276-4421-A301-3163452C016D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>Расположение</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>Тег</t>
-  </si>
-  <si>
-    <t>Десктопный редактор Р7-Офис -&gt; Смоук тест -&gt; Проверка базового функционала (Smoke)</t>
   </si>
   <si>
     <t/>
@@ -82,6 +79,15 @@
   <si>
     <t>Текст введён.
 Выровнен по левому краю.</t>
+  </si>
+  <si>
+    <t>Smoke</t>
+  </si>
+  <si>
+    <t>Критичность</t>
+  </si>
+  <si>
+    <t>HIGH</t>
   </si>
 </sst>
 </file>
@@ -128,7 +134,19 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -142,9 +160,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G5" totalsRowShown="0">
-  <autoFilter ref="A1:G5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:H5" totalsRowShown="0">
+  <autoFilter ref="A1:H5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="8">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Расположение"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Наименование"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Предусловия"/>
@@ -152,6 +170,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Постусловия"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Ожидаемый результат"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Тег"/>
+    <tableColumn id="1" xr3:uid="{FDA97CF4-E99C-4F79-BD3B-1F5287E23D5C}" name="Критичность" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -442,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="50.6640625" style="2" customWidth="1"/>
@@ -455,7 +474,7 @@
     <col min="9" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -477,98 +496,107 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="str">
         <f>HYPERLINK("https://team-n7lk.testit.software/projects/1/tests/16", "Ввод текста в редакторе документов")</f>
         <v>Ввод текста в редакторе документов</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
+    <row r="5" spans="1:8" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
+      <c r="H5" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
